--- a/uniStatsData.xlsx
+++ b/uniStatsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/Projects/rateByProfessor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3E62D75-2545-3D4D-A0F4-A383CE1A2751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A3B3C-23CD-3648-B4C7-7082D8A971B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{281806DB-6A5C-954B-AFC4-116CE57D75F1}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="2323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="2322">
   <si>
     <t>course</t>
   </si>
@@ -6952,15 +6952,9 @@
     <t>University of Auckland</t>
   </si>
   <si>
-    <t>Finance</t>
-  </si>
-  <si>
     <t>AUT</t>
   </si>
   <si>
-    <t>Accounting</t>
-  </si>
-  <si>
     <t>Professor ID</t>
   </si>
   <si>
@@ -7007,6 +7001,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>ACCOUNTING</t>
   </si>
 </sst>
 </file>
@@ -50839,19 +50836,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C1" t="s">
         <v>2307</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>2308</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2309</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2310</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -50859,13 +50856,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2303</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2304</v>
+        <v>347</v>
       </c>
       <c r="E2" s="1">
         <v>5</v>
@@ -50876,13 +50873,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2304</v>
+        <v>347</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -50893,13 +50890,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2306</v>
+        <v>2321</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -50917,16 +50914,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2312</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2311</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2313</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2314</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -50937,10 +50934,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -50951,10 +50948,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="D3" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -50965,10 +50962,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="D4" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
     </row>
   </sheetData>

--- a/uniStatsData.xlsx
+++ b/uniStatsData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/Projects/rateByProfessor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/Projects/MAC-AWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A3B3C-23CD-3648-B4C7-7082D8A971B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C1DE3B-7A1C-7347-8408-373178B9892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{281806DB-6A5C-954B-AFC4-116CE57D75F1}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{281806DB-6A5C-954B-AFC4-116CE57D75F1}"/>
   </bookViews>
   <sheets>
     <sheet name="courseData" sheetId="1" r:id="rId1"/>
@@ -48152,7 +48152,7 @@
         <v>100</v>
       </c>
       <c r="C2038" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D2038" s="2">
         <v>0.37</v>
@@ -48172,7 +48172,7 @@
         <v>100</v>
       </c>
       <c r="C2039" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D2039" s="2">
         <v>0.22</v>
@@ -49732,7 +49732,7 @@
         <v>100</v>
       </c>
       <c r="C2117" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D2117" s="2">
         <v>0.13</v>
@@ -49752,7 +49752,7 @@
         <v>100</v>
       </c>
       <c r="C2118" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D2118" s="2">
         <v>0.08</v>

--- a/uniStatsData.xlsx
+++ b/uniStatsData.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/Projects/MAC-AWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C1DE3B-7A1C-7347-8408-373178B9892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D53ED4-9F63-2648-9198-646BF2C7EAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{281806DB-6A5C-954B-AFC4-116CE57D75F1}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{281806DB-6A5C-954B-AFC4-116CE57D75F1}"/>
   </bookViews>
   <sheets>
     <sheet name="courseData" sheetId="1" r:id="rId1"/>
     <sheet name="professors" sheetId="2" r:id="rId2"/>
     <sheet name="ratings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="2322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="2324">
   <si>
     <t>course</t>
   </si>
@@ -6976,41 +6976,47 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>examplename1</t>
-  </si>
-  <si>
-    <t>examplename2</t>
-  </si>
-  <si>
-    <t>examplename3</t>
-  </si>
-  <si>
     <t>okay</t>
   </si>
   <si>
-    <t>tmac425@aucklanduni.ac.nz</t>
-  </si>
-  <si>
     <t>shit</t>
   </si>
   <si>
-    <t>ewuigf</t>
-  </si>
-  <si>
     <t>good</t>
   </si>
   <si>
-    <t>ACCOUNTING</t>
+    <t>Steven Hawking</t>
+  </si>
+  <si>
+    <t>Thomas Bayes</t>
+  </si>
+  <si>
+    <t>Enrico Fermi</t>
+  </si>
+  <si>
+    <t>Ernest Rutherford</t>
+  </si>
+  <si>
+    <t>University of Canterbury</t>
+  </si>
+  <si>
+    <t>Warren Buffet</t>
+  </si>
+  <si>
+    <t>boring</t>
+  </si>
+  <si>
+    <t>idiot</t>
+  </si>
+  <si>
+    <t>pretty good</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -7023,14 +7029,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -7056,19 +7054,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -50831,7 +50826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDF04F-A50E-CF4C-A5A3-C31B43F6D8E1}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -50856,15 +50851,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2303</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>347</v>
+        <v>544</v>
       </c>
       <c r="E2" s="1">
+        <f>AVERAGEIF(ratings!A:A,professors!A2,ratings!B:B)</f>
         <v>5</v>
       </c>
     </row>
@@ -50873,16 +50869,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>347</v>
+        <v>544</v>
       </c>
       <c r="E3" s="1">
-        <v>5</v>
+        <f>AVERAGEIF(ratings!A:A,professors!A3,ratings!B:B)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -50890,16 +50887,53 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2304</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2321</v>
+        <v>725</v>
       </c>
       <c r="E4" s="1">
+        <f>AVERAGEIF(ratings!A:A,professors!A4,ratings!B:B)</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="E5" s="1">
+        <f>AVERAGEIF(ratings!A:A,professors!A5,ratings!B:B)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E6" s="1">
+        <f>AVERAGEIF(ratings!A:A,professors!A6,ratings!B:B)</f>
+        <v>6.666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -50909,10 +50943,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD71EBF-3B15-E54C-BD25-F2CBFD95912C}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2310</v>
       </c>
@@ -50922,11 +50956,8 @@
       <c r="C1" s="1" t="s">
         <v>2311</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -50934,27 +50965,21 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>2316</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>2317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2318</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2319</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -50962,16 +50987,51 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>2320</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2319</v>
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2323</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{04A2F8B1-6E9B-834B-9034-54C5D5EA22C4}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>